--- a/exports/trend_1d/COFORGE_full_report.xlsx
+++ b/exports/trend_1d/COFORGE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:U64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.6</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42082</v>
+        <v>42083</v>
       </c>
       <c r="H2" t="n">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="I2" t="n">
         <v>75.49723868563422</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K2" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>9.33</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>16.04</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42128</v>
+        <v>42129</v>
       </c>
       <c r="H3" t="n">
-        <v>71.5</v>
+        <v>80.5</v>
       </c>
       <c r="I3" t="n">
         <v>79.37087973476187</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K3" t="n">
-        <v>4.67</v>
+        <v>-7.33</v>
       </c>
       <c r="L3" t="n">
-        <v>5.33</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
         <v>2.86</v>
       </c>
       <c r="N3" t="n">
-        <v>4.29</v>
+        <v>12.59</v>
       </c>
       <c r="O3" t="n">
         <v>-3.23</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>24.11</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42240</v>
+        <v>42241</v>
       </c>
       <c r="H4" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I4" t="n">
         <v>90.95422993476166</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K4" t="n">
-        <v>13.04</v>
+        <v>8.07</v>
       </c>
       <c r="L4" t="n">
         <v>19.25</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>21.65</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42293</v>
+        <v>42296</v>
       </c>
       <c r="H5" t="n">
-        <v>98.5</v>
+        <v>112</v>
       </c>
       <c r="I5" t="n">
         <v>99.80920005170465</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K5" t="n">
-        <v>-13.22</v>
+        <v>-28.74</v>
       </c>
       <c r="L5" t="n">
-        <v>16.67</v>
+        <v>31.61</v>
       </c>
       <c r="M5" t="n">
         <v>1.68</v>
       </c>
       <c r="N5" t="n">
-        <v>8.09</v>
+        <v>13.71</v>
       </c>
       <c r="O5" t="n">
         <v>-4.4</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>20.69</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H6" t="n">
-        <v>114</v>
+        <v>107.5</v>
       </c>
       <c r="I6" t="n">
         <v>108.4856609624702</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K6" t="n">
-        <v>1.79</v>
+        <v>-4.02</v>
       </c>
       <c r="L6" t="n">
         <v>14.29</v>
@@ -783,7 +854,7 @@
         <v>4.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.02</v>
+        <v>5.7</v>
       </c>
       <c r="O6" t="n">
         <v>13.71</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.79</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42461</v>
+        <v>42464</v>
       </c>
       <c r="H7" t="n">
-        <v>99</v>
+        <v>101.5</v>
       </c>
       <c r="I7" t="n">
         <v>101.0780057180861</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K7" t="n">
-        <v>7.91</v>
+        <v>5.58</v>
       </c>
       <c r="L7" t="n">
         <v>10.23</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.53</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42545</v>
+        <v>42548</v>
       </c>
       <c r="H8" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="I8" t="n">
         <v>101.4918703129904</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="L8" t="n">
         <v>10.84</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.44</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42635</v>
+        <v>42636</v>
       </c>
       <c r="H9" t="n">
-        <v>82.5</v>
+        <v>86.5</v>
       </c>
       <c r="I9" t="n">
         <v>85.11319533217245</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K9" t="n">
-        <v>17.91</v>
+        <v>13.93</v>
       </c>
       <c r="L9" t="n">
         <v>6.47</v>
@@ -954,7 +1061,7 @@
         <v>1.49</v>
       </c>
       <c r="N9" t="n">
-        <v>3.02</v>
+        <v>4.85</v>
       </c>
       <c r="O9" t="n">
         <v>-0.99</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.9</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42676</v>
+        <v>42677</v>
       </c>
       <c r="H10" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I10" t="n">
         <v>80.21687079171923</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.36</v>
+        <v>-8.67</v>
       </c>
       <c r="L10" t="n">
         <v>10.4</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>13.38</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42754</v>
+        <v>42755</v>
       </c>
       <c r="H11" t="n">
-        <v>88</v>
+        <v>88.5</v>
       </c>
       <c r="I11" t="n">
         <v>88.0875579388035</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.39</v>
+        <v>-12.03</v>
       </c>
       <c r="L11" t="n">
-        <v>13.29</v>
+        <v>14.56</v>
       </c>
       <c r="M11" t="n">
         <v>1.27</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.76</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42941</v>
+        <v>42942</v>
       </c>
       <c r="H12" t="n">
-        <v>105.5</v>
+        <v>104.5</v>
       </c>
       <c r="I12" t="n">
         <v>104.7692666447097</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K12" t="n">
-        <v>19.21</v>
+        <v>18.08</v>
       </c>
       <c r="L12" t="n">
         <v>9.6</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.06</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42997</v>
+        <v>42998</v>
       </c>
       <c r="H13" t="n">
-        <v>101</v>
+        <v>106.5</v>
       </c>
       <c r="I13" t="n">
         <v>105.5392823742388</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>-1.91</v>
       </c>
       <c r="L13" t="n">
         <v>2.39</v>
@@ -1182,7 +1337,7 @@
         <v>1.51</v>
       </c>
       <c r="N13" t="n">
-        <v>3.02</v>
+        <v>5.45</v>
       </c>
       <c r="O13" t="n">
         <v>-0.95</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.27</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43150</v>
+        <v>43151</v>
       </c>
       <c r="H14" t="n">
-        <v>152.5</v>
+        <v>151.5</v>
       </c>
       <c r="I14" t="n">
         <v>151.8592409527855</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K14" t="n">
-        <v>43.19</v>
+        <v>42.25</v>
       </c>
       <c r="L14" t="n">
         <v>6.57</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>16.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43168</v>
+        <v>43171</v>
       </c>
       <c r="H15" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I15" t="n">
         <v>176.1296700509016</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>-16.17</v>
+        <v>-20.13</v>
       </c>
       <c r="L15" t="n">
-        <v>17.49</v>
+        <v>20.79</v>
       </c>
       <c r="M15" t="n">
         <v>1.42</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>11.74</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43361</v>
+        <v>43362</v>
       </c>
       <c r="H16" t="n">
-        <v>261.5</v>
+        <v>254.5</v>
       </c>
       <c r="I16" t="n">
         <v>255.8362802216695</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K16" t="n">
-        <v>43.68</v>
+        <v>39.84</v>
       </c>
       <c r="L16" t="n">
         <v>9.890000000000001</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>13.59</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43476</v>
+        <v>43479</v>
       </c>
       <c r="H17" t="n">
-        <v>232.5</v>
+        <v>237.5</v>
       </c>
       <c r="I17" t="n">
         <v>236.2776629500044</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K17" t="n">
-        <v>8.640000000000001</v>
+        <v>6.68</v>
       </c>
       <c r="L17" t="n">
         <v>4.52</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43587</v>
+        <v>43588</v>
       </c>
       <c r="H18" t="n">
-        <v>256.5</v>
+        <v>253.5</v>
       </c>
       <c r="I18" t="n">
         <v>253.8316239167191</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>6.74</v>
       </c>
       <c r="L18" t="n">
         <v>3.37</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.4</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43614</v>
+        <v>43615</v>
       </c>
       <c r="H19" t="n">
-        <v>257</v>
+        <v>261.5</v>
       </c>
       <c r="I19" t="n">
         <v>260.3845449102297</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.38</v>
+        <v>-3.16</v>
       </c>
       <c r="L19" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="M19" t="n">
         <v>1.58</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>5.88</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43671</v>
+        <v>43672</v>
       </c>
       <c r="H20" t="n">
-        <v>266.5</v>
+        <v>255</v>
       </c>
       <c r="I20" t="n">
         <v>258.8945702678459</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K20" t="n">
-        <v>1.91</v>
+        <v>-2.49</v>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>5.93</v>
       </c>
       <c r="M20" t="n">
         <v>2.42</v>
       </c>
       <c r="N20" t="n">
-        <v>1.51</v>
+        <v>4.32</v>
       </c>
       <c r="O20" t="n">
         <v>1.75</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.51</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43685</v>
+        <v>43686</v>
       </c>
       <c r="H21" t="n">
-        <v>255.5</v>
+        <v>260</v>
       </c>
       <c r="I21" t="n">
         <v>259.7893832201514</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2</v>
+        <v>-1.96</v>
       </c>
       <c r="L21" t="n">
         <v>3.73</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.64</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43808</v>
+        <v>43809</v>
       </c>
       <c r="H22" t="n">
-        <v>295</v>
+        <v>287.5</v>
       </c>
       <c r="I22" t="n">
         <v>288.2021751049233</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K22" t="n">
-        <v>13.46</v>
+        <v>10.58</v>
       </c>
       <c r="L22" t="n">
         <v>3.27</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43815</v>
+        <v>43816</v>
       </c>
       <c r="H23" t="n">
-        <v>294.5</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>313.9626428918946</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.43</v>
+        <v>-11.65</v>
       </c>
       <c r="L23" t="n">
-        <v>5.22</v>
+        <v>14.26</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.48</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
         <v>-2.54</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>12.39</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H24" t="n">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="I24" t="n">
         <v>358.0588063194037</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K24" t="n">
-        <v>17.45</v>
+        <v>5.3</v>
       </c>
       <c r="L24" t="n">
         <v>7.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>4.64</v>
+        <v>10.34</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>18.4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43956</v>
+        <v>43957</v>
       </c>
       <c r="H25" t="n">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="I25" t="n">
         <v>272.0838110858336</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K25" t="n">
-        <v>29.59</v>
+        <v>15.98</v>
       </c>
       <c r="L25" t="n">
         <v>17.46</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>28.79</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44127</v>
+        <v>44130</v>
       </c>
       <c r="H26" t="n">
-        <v>476</v>
+        <v>442.5</v>
       </c>
       <c r="I26" t="n">
         <v>473.5548272381771</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K26" t="n">
-        <v>67.61</v>
+        <v>55.81</v>
       </c>
       <c r="L26" t="n">
         <v>13.73</v>
@@ -1923,7 +2234,7 @@
         <v>4.75</v>
       </c>
       <c r="N26" t="n">
-        <v>6.79</v>
+        <v>7.04</v>
       </c>
       <c r="O26" t="n">
         <v>19.33</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>23.08</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44173</v>
+        <v>44174</v>
       </c>
       <c r="H27" t="n">
-        <v>495.5</v>
+        <v>501.5</v>
       </c>
       <c r="I27" t="n">
         <v>498.2610261341197</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K27" t="n">
-        <v>-11.98</v>
+        <v>-13.33</v>
       </c>
       <c r="L27" t="n">
-        <v>13.67</v>
+        <v>15.93</v>
       </c>
       <c r="M27" t="n">
         <v>1.72</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H28" t="n">
-        <v>527.5</v>
+        <v>502</v>
       </c>
       <c r="I28" t="n">
         <v>514.5434308886669</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>5.18</v>
+        <v>0.1</v>
       </c>
       <c r="L28" t="n">
         <v>8.08</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>15.61</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44264</v>
+        <v>44265</v>
       </c>
       <c r="H29" t="n">
-        <v>516.5</v>
+        <v>547</v>
       </c>
       <c r="I29" t="n">
         <v>546.9261403535447</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.89</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L29" t="n">
         <v>9.960000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3</v>
+        <v>5.91</v>
       </c>
       <c r="O29" t="n">
         <v>-4.83</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>13.94</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H30" t="n">
-        <v>1079.5</v>
+        <v>1014</v>
       </c>
       <c r="I30" t="n">
         <v>1041.020666074748</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K30" t="n">
-        <v>97.34999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="L30" t="n">
         <v>4.2</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>153</v>
+        <v>154</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>17.63</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44516</v>
+        <v>44517</v>
       </c>
       <c r="H31" t="n">
-        <v>1144.5</v>
+        <v>1168</v>
       </c>
       <c r="I31" t="n">
         <v>1146.749888643851</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K31" t="n">
-        <v>-12.87</v>
+        <v>-15.19</v>
       </c>
       <c r="L31" t="n">
-        <v>15.88</v>
+        <v>17.11</v>
       </c>
       <c r="M31" t="n">
         <v>1.91</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.23</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44533</v>
+        <v>44536</v>
       </c>
       <c r="H32" t="n">
-        <v>1070</v>
+        <v>1025</v>
       </c>
       <c r="I32" t="n">
         <v>1036.864865765171</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>-8.390000000000001</v>
+        <v>-12.24</v>
       </c>
       <c r="L32" t="n">
         <v>13.83</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.82</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44559</v>
+        <v>44560</v>
       </c>
       <c r="H33" t="n">
-        <v>1130</v>
+        <v>1172</v>
       </c>
       <c r="I33" t="n">
         <v>1160.879125262145</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K33" t="n">
-        <v>-10.24</v>
+        <v>-14.34</v>
       </c>
       <c r="L33" t="n">
-        <v>11.85</v>
+        <v>15.32</v>
       </c>
       <c r="M33" t="n">
         <v>1.78</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>10.83</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44578</v>
+        <v>44579</v>
       </c>
       <c r="H34" t="n">
-        <v>1125.5</v>
+        <v>1082</v>
       </c>
       <c r="I34" t="n">
         <v>1112.133470457358</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.97</v>
+        <v>-7.68</v>
       </c>
       <c r="L34" t="n">
-        <v>5.12</v>
+        <v>8.15</v>
       </c>
       <c r="M34" t="n">
         <v>1.52</v>
       </c>
       <c r="N34" t="n">
-        <v>3.04</v>
+        <v>3.86</v>
       </c>
       <c r="O34" t="n">
         <v>3.72</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.63</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44736</v>
+        <v>44739</v>
       </c>
       <c r="H35" t="n">
-        <v>729.5</v>
+        <v>758</v>
       </c>
       <c r="I35" t="n">
         <v>747.513859596173</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K35" t="n">
-        <v>32.58</v>
+        <v>29.94</v>
       </c>
       <c r="L35" t="n">
         <v>4.9</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>13.92</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44799</v>
+        <v>44802</v>
       </c>
       <c r="H36" t="n">
-        <v>732.5</v>
+        <v>702.5</v>
       </c>
       <c r="I36" t="n">
         <v>722.9332460057922</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.36</v>
+        <v>-7.32</v>
       </c>
       <c r="L36" t="n">
         <v>12.07</v>
       </c>
       <c r="M36" t="n">
-        <v>2.72</v>
+        <v>6.35</v>
       </c>
       <c r="N36" t="n">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="O36" t="n">
         <v>3.91</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.39</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H37" t="n">
-        <v>696</v>
+        <v>724.5</v>
       </c>
       <c r="I37" t="n">
         <v>716.6644821902863</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K37" t="n">
-        <v>0.93</v>
+        <v>-3.13</v>
       </c>
       <c r="L37" t="n">
         <v>4.2</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.46</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44903</v>
+        <v>44904</v>
       </c>
       <c r="H38" t="n">
-        <v>797</v>
+        <v>775.5</v>
       </c>
       <c r="I38" t="n">
         <v>780.8848560922905</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K38" t="n">
-        <v>10.01</v>
+        <v>7.04</v>
       </c>
       <c r="L38" t="n">
         <v>3.52</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.49</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44946</v>
+        <v>44949</v>
       </c>
       <c r="H39" t="n">
-        <v>820.5</v>
+        <v>872</v>
       </c>
       <c r="I39" t="n">
         <v>821.3843265993268</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.8</v>
+        <v>-12.44</v>
       </c>
       <c r="L39" t="n">
-        <v>9.609999999999999</v>
+        <v>13.93</v>
       </c>
       <c r="M39" t="n">
         <v>1.83</v>
       </c>
       <c r="N39" t="n">
-        <v>3.4</v>
+        <v>6.28</v>
       </c>
       <c r="O39" t="n">
         <v>-2.7</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>12.84</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44998</v>
+        <v>44999</v>
       </c>
       <c r="H40" t="n">
-        <v>817</v>
+        <v>784.5</v>
       </c>
       <c r="I40" t="n">
         <v>807.7549631411633</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.31</v>
+        <v>-10.03</v>
       </c>
       <c r="L40" t="n">
-        <v>8.26</v>
+        <v>11.81</v>
       </c>
       <c r="M40" t="n">
         <v>6.57</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>10.42</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45019</v>
+        <v>45021</v>
       </c>
       <c r="H41" t="n">
-        <v>770.5</v>
+        <v>816</v>
       </c>
       <c r="I41" t="n">
         <v>791.8868878289892</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K41" t="n">
-        <v>1.78</v>
+        <v>-4.02</v>
       </c>
       <c r="L41" t="n">
-        <v>4.53</v>
+        <v>5.04</v>
       </c>
       <c r="M41" t="n">
         <v>1.28</v>
       </c>
       <c r="N41" t="n">
-        <v>4.23</v>
+        <v>5.91</v>
       </c>
       <c r="O41" t="n">
         <v>-3.98</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.66</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45160</v>
+        <v>45161</v>
       </c>
       <c r="H42" t="n">
-        <v>992</v>
+        <v>982.5</v>
       </c>
       <c r="I42" t="n">
         <v>982.6164490486606</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K42" t="n">
-        <v>21.57</v>
+        <v>20.4</v>
       </c>
       <c r="L42" t="n">
         <v>8.029999999999999</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.81</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45161</v>
+        <v>45162</v>
       </c>
       <c r="H43" t="n">
-        <v>982.5</v>
+        <v>1078</v>
       </c>
       <c r="I43" t="n">
         <v>1069.096390451131</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>1.78</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M43" t="n">
         <v>0.4</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="O43" t="n">
         <v>-0.96</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>17.12</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45196</v>
+        <v>45197</v>
       </c>
       <c r="H44" t="n">
-        <v>1041</v>
+        <v>1024.5</v>
       </c>
       <c r="I44" t="n">
         <v>1031.834485923534</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.43</v>
+        <v>-4.96</v>
       </c>
       <c r="L44" t="n">
         <v>12.76</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H45" t="n">
-        <v>1017</v>
+        <v>1068.5</v>
       </c>
       <c r="I45" t="n">
         <v>1054.577932970124</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K45" t="n">
-        <v>0.73</v>
+        <v>-4.29</v>
       </c>
       <c r="L45" t="n">
-        <v>3.12</v>
+        <v>4.54</v>
       </c>
       <c r="M45" t="n">
-        <v>0.99</v>
+        <v>1.18</v>
       </c>
       <c r="N45" t="n">
-        <v>2.14</v>
+        <v>5.06</v>
       </c>
       <c r="O45" t="n">
         <v>-1.59</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45364</v>
+        <v>45365</v>
       </c>
       <c r="H46" t="n">
-        <v>1234.5</v>
+        <v>1217.5</v>
       </c>
       <c r="I46" t="n">
         <v>1222.660608508407</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K46" t="n">
-        <v>15.54</v>
+        <v>13.94</v>
       </c>
       <c r="L46" t="n">
         <v>4.07</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="H47" t="n">
-        <v>958</v>
+        <v>982</v>
       </c>
       <c r="I47" t="n">
         <v>968.6237229946108</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K47" t="n">
-        <v>21.31</v>
+        <v>19.34</v>
       </c>
       <c r="L47" t="n">
         <v>1.03</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.01</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45583</v>
+        <v>45586</v>
       </c>
       <c r="H48" t="n">
-        <v>1442</v>
+        <v>1365</v>
       </c>
       <c r="I48" t="n">
         <v>1389.755504518604</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K48" t="n">
-        <v>46.84</v>
+        <v>39</v>
       </c>
       <c r="L48" t="n">
         <v>3.82</v>
@@ -3177,7 +3752,7 @@
         <v>4.61</v>
       </c>
       <c r="N48" t="n">
-        <v>3.87</v>
+        <v>5.34</v>
       </c>
       <c r="O48" t="n">
         <v>2.51</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>6</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>11.91</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="H49" t="n">
-        <v>1360</v>
+        <v>1511.5</v>
       </c>
       <c r="I49" t="n">
         <v>1493.29142713681</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>0.37</v>
+        <v>-10.73</v>
       </c>
       <c r="L49" t="n">
-        <v>6.04</v>
+        <v>12.05</v>
       </c>
       <c r="M49" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.21</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>11.14</v>
       </c>
       <c r="O49" t="n">
         <v>-5.34</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>14.62</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H50" t="n">
-        <v>1881</v>
+        <v>1741</v>
       </c>
       <c r="I50" t="n">
         <v>1794.601618685876</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K50" t="n">
-        <v>24.45</v>
+        <v>15.18</v>
       </c>
       <c r="L50" t="n">
         <v>8.24</v>
@@ -3291,7 +3890,7 @@
         <v>3.01</v>
       </c>
       <c r="N50" t="n">
-        <v>2.98</v>
+        <v>7.44</v>
       </c>
       <c r="O50" t="n">
         <v>11.14</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>13.62</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45679</v>
+        <v>45680</v>
       </c>
       <c r="H51" t="n">
-        <v>1645.5</v>
+        <v>1839.5</v>
       </c>
       <c r="I51" t="n">
         <v>1829.436656260724</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>5.49</v>
+        <v>-5.66</v>
       </c>
       <c r="L51" t="n">
         <v>7.09</v>
       </c>
       <c r="M51" t="n">
-        <v>0.67</v>
+        <v>5.86</v>
       </c>
       <c r="N51" t="n">
-        <v>1.75</v>
+        <v>11.79</v>
       </c>
       <c r="O51" t="n">
         <v>-7.44</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>14.6</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H52" t="n">
-        <v>1653</v>
+        <v>1615.5</v>
       </c>
       <c r="I52" t="n">
         <v>1625.068808428814</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K52" t="n">
-        <v>-10.14</v>
+        <v>-12.18</v>
       </c>
       <c r="L52" t="n">
-        <v>10.79</v>
+        <v>12.91</v>
       </c>
       <c r="M52" t="n">
         <v>1.52</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>15.46</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H53" t="n">
-        <v>1391</v>
+        <v>1478.5</v>
       </c>
       <c r="I53" t="n">
         <v>1460.068011499138</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K53" t="n">
-        <v>13.9</v>
+        <v>8.48</v>
       </c>
       <c r="L53" t="n">
         <v>6.78</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>15.33</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45861</v>
+        <v>45862</v>
       </c>
       <c r="H54" t="n">
-        <v>1849.7</v>
+        <v>1676</v>
       </c>
       <c r="I54" t="n">
         <v>1831.016955570387</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K54" t="n">
-        <v>25.11</v>
+        <v>13.36</v>
       </c>
       <c r="L54" t="n">
         <v>3.45</v>
@@ -3519,7 +4166,7 @@
         <v>2.58</v>
       </c>
       <c r="N54" t="n">
-        <v>2.4</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O54" t="n">
         <v>6.29</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>14.53</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H55" t="n">
-        <v>1779.6</v>
+        <v>1791.9</v>
       </c>
       <c r="I55" t="n">
         <v>1786.257523878711</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.18</v>
+        <v>-6.92</v>
       </c>
       <c r="L55" t="n">
         <v>9.640000000000001</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>7</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="H56" t="n">
-        <v>1716.9</v>
+        <v>1667.9</v>
       </c>
       <c r="I56" t="n">
         <v>1686.120737514891</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.19</v>
+        <v>-6.92</v>
       </c>
       <c r="L56" t="n">
-        <v>5.01</v>
+        <v>7.24</v>
       </c>
       <c r="M56" t="n">
         <v>4.19</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>10.29</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="H57" t="n">
-        <v>1686.5</v>
+        <v>1713.7</v>
       </c>
       <c r="I57" t="n">
         <v>1704.621535815914</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.12</v>
+        <v>-2.75</v>
       </c>
       <c r="L57" t="n">
-        <v>3.32</v>
+        <v>3.92</v>
       </c>
       <c r="M57" t="n">
         <v>2.04</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.74</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="H58" t="n">
-        <v>1873.5</v>
+        <v>1820.2</v>
       </c>
       <c r="I58" t="n">
         <v>1844.309683888032</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K58" t="n">
-        <v>9.32</v>
+        <v>6.21</v>
       </c>
       <c r="L58" t="n">
         <v>2.36</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>10.3</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H59" t="n">
-        <v>1153.9</v>
+        <v>1213.4</v>
       </c>
       <c r="I59" t="n">
         <v>1208.595573278343</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K59" t="n">
-        <v>36.61</v>
+        <v>33.34</v>
       </c>
       <c r="L59" t="n">
         <v>3.78</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>16.71</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H60" t="n">
-        <v>1220.6</v>
+        <v>1150.9</v>
       </c>
       <c r="I60" t="n">
         <v>1161.063061761074</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K60" t="n">
-        <v>0.59</v>
+        <v>-5.15</v>
       </c>
       <c r="L60" t="n">
         <v>6.87</v>
@@ -3861,7 +4580,7 @@
         <v>1.79</v>
       </c>
       <c r="N60" t="n">
-        <v>4.41</v>
+        <v>5.71</v>
       </c>
       <c r="O60" t="n">
         <v>5.16</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>15.59</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H61" t="n">
-        <v>1285.3</v>
+        <v>1368.1</v>
       </c>
       <c r="I61" t="n">
         <v>1301.947080940475</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>-11.68</v>
+        <v>-18.87</v>
       </c>
       <c r="L61" t="n">
-        <v>14.05</v>
+        <v>19.38</v>
       </c>
       <c r="M61" t="n">
         <v>7.91</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>15.63</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="H62" t="n">
-        <v>1845</v>
+        <v>1833.1</v>
       </c>
       <c r="I62" t="n">
         <v>1843.158231203105</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K62" t="n">
-        <v>34.86</v>
+        <v>33.99</v>
       </c>
       <c r="L62" t="n">
         <v>8.65</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>10.59</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H63" t="n">
-        <v>1928</v>
+        <v>1934.3</v>
       </c>
       <c r="I63" t="n">
         <v>1929.396447262828</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.18</v>
+        <v>-5.52</v>
       </c>
       <c r="L63" t="n">
-        <v>7.19</v>
+        <v>7.47</v>
       </c>
       <c r="M63" t="n">
         <v>2.21</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4092,6 +4859,14 @@
       <c r="Q64" t="n">
         <v>9</v>
       </c>
+      <c r="R64" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9050,7 +9825,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.7</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="6">
@@ -9060,7 +9835,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="7">
@@ -9070,7 +9845,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
@@ -9080,7 +9855,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -9090,7 +9865,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -9100,7 +9875,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>150.8</v>
       </c>
     </row>
     <row r="11">
@@ -9140,7 +9915,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.880000000000001</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="15">
@@ -9150,7 +9925,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.4</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="16">
@@ -9160,7 +9935,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.36</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="17">
@@ -9170,7 +9945,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>97.34999999999999</v>
+        <v>85.37</v>
       </c>
     </row>
     <row r="18">
@@ -9180,7 +9955,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59.7</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="19">
@@ -9190,7 +9965,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.94</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="20">
@@ -9200,7 +9975,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.05</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -9210,7 +9985,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.25</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="22">
@@ -9220,7 +9995,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
@@ -9230,7 +10005,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -9240,7 +10015,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.76</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="25">
@@ -9260,7 +10035,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.83</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="27">
@@ -9280,7 +10055,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
